--- a/backend/data/financials_by_company/1433.HK.xlsx
+++ b/backend/data/financials_by_company/1433.HK.xlsx
@@ -657,196 +657,192 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>21844</v>
+        <v>201190</v>
       </c>
       <c r="C2" t="n">
-        <v>0.172</v>
+        <v>0.295</v>
       </c>
       <c r="D2" t="n">
-        <v>110805000</v>
+        <v>49894000</v>
       </c>
       <c r="E2" t="n">
-        <v>127000</v>
+        <v>682000</v>
       </c>
       <c r="F2" t="n">
-        <v>127000</v>
+        <v>682000</v>
       </c>
       <c r="G2" t="n">
-        <v>61859000</v>
+        <v>14984000</v>
       </c>
       <c r="H2" t="n">
-        <v>33821000</v>
+        <v>27069000</v>
       </c>
       <c r="I2" t="n">
-        <v>280430000</v>
+        <v>204503000</v>
       </c>
       <c r="J2" t="n">
-        <v>110932000</v>
+        <v>50576000</v>
       </c>
       <c r="K2" t="n">
-        <v>77111000</v>
+        <v>23507000</v>
       </c>
       <c r="L2" t="n">
-        <v>-1922000</v>
+        <v>-1989000</v>
       </c>
       <c r="M2" t="n">
-        <v>2364000</v>
+        <v>2253000</v>
       </c>
       <c r="N2" t="n">
-        <v>442000</v>
+        <v>264000</v>
       </c>
       <c r="O2" t="n">
-        <v>61753844</v>
+        <v>14503190</v>
       </c>
       <c r="P2" t="n">
-        <v>61859000</v>
+        <v>14984000</v>
       </c>
       <c r="Q2" t="n">
-        <v>477617000</v>
+        <v>342907000</v>
       </c>
       <c r="R2" t="n">
-        <v>1995453825</v>
+        <v>2000000000</v>
       </c>
       <c r="S2" t="n">
-        <v>1995453825</v>
+        <v>2000000000</v>
       </c>
       <c r="T2" t="n">
-        <v>0.031</v>
+        <v>0.0075</v>
       </c>
       <c r="U2" t="n">
-        <v>0.031</v>
+        <v>0.0075</v>
       </c>
       <c r="V2" t="n">
-        <v>61859000</v>
+        <v>14984000</v>
       </c>
       <c r="W2" t="n">
-        <v>61859000</v>
+        <v>14984000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>61859000</v>
+        <v>14984000</v>
       </c>
       <c r="Z2" t="n">
-        <v>61859000</v>
+        <v>14984000</v>
       </c>
       <c r="AA2" t="n">
-        <v>61859000</v>
+        <v>14984000</v>
       </c>
       <c r="AB2" t="n">
-        <v>12888000</v>
+        <v>6270000</v>
       </c>
       <c r="AC2" t="n">
-        <v>74747000</v>
+        <v>21254000</v>
       </c>
       <c r="AD2" t="n">
-        <v>3002000</v>
+        <v>2955000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
+        <v>487000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-487000</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>-1922000</v>
+        <v>-1989000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2364000</v>
+        <v>2253000</v>
       </c>
       <c r="AK2" t="n">
-        <v>442000</v>
+        <v>264000</v>
       </c>
       <c r="AL2" t="n">
-        <v>73432000</v>
+        <v>19606000</v>
       </c>
       <c r="AM2" t="n">
-        <v>197187000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2433000</v>
-      </c>
+        <v>138404000</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>196881000</v>
+        <v>140933000</v>
       </c>
       <c r="AP2" t="n">
-        <v>61243000</v>
+        <v>45790000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>135638000</v>
+        <v>95143000</v>
       </c>
       <c r="AR2" t="n">
-        <v>270619000</v>
+        <v>158010000</v>
       </c>
       <c r="AS2" t="n">
-        <v>280430000</v>
+        <v>204503000</v>
       </c>
       <c r="AT2" t="n">
-        <v>551049000</v>
+        <v>362513000</v>
       </c>
       <c r="AU2" t="n">
-        <v>551049000</v>
+        <v>362513000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-1982000</v>
+        <v>-382967</v>
       </c>
       <c r="C3" t="n">
-        <v>0.25</v>
+        <v>0.331</v>
       </c>
       <c r="D3" t="n">
-        <v>22358000</v>
+        <v>48299000</v>
       </c>
       <c r="E3" t="n">
-        <v>-7567000</v>
+        <v>377000</v>
       </c>
       <c r="F3" t="n">
-        <v>-7928000</v>
+        <v>-1157000</v>
       </c>
       <c r="G3" t="n">
-        <v>-25676000</v>
+        <v>12558000</v>
       </c>
       <c r="H3" t="n">
-        <v>31277000</v>
+        <v>27697000</v>
       </c>
       <c r="I3" t="n">
-        <v>209757000</v>
+        <v>235116000</v>
       </c>
       <c r="J3" t="n">
-        <v>14791000</v>
+        <v>48676000</v>
       </c>
       <c r="K3" t="n">
-        <v>-16486000</v>
+        <v>20979000</v>
       </c>
       <c r="L3" t="n">
-        <v>-2512000</v>
+        <v>-1732000</v>
       </c>
       <c r="M3" t="n">
-        <v>3164000</v>
+        <v>2203000</v>
       </c>
       <c r="N3" t="n">
-        <v>652000</v>
+        <v>471000</v>
       </c>
       <c r="O3" t="n">
-        <v>-19369000</v>
+        <v>14866033</v>
       </c>
       <c r="P3" t="n">
-        <v>-25676000</v>
+        <v>12558000</v>
       </c>
       <c r="Q3" t="n">
-        <v>384105000</v>
+        <v>390820000</v>
       </c>
       <c r="R3" t="n">
         <v>2000000000</v>
@@ -855,137 +851,139 @@
         <v>2000000000</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0128</v>
+        <v>0.0063</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0128</v>
+        <v>0.0063</v>
       </c>
       <c r="V3" t="n">
-        <v>-25676000</v>
+        <v>12558000</v>
       </c>
       <c r="W3" t="n">
-        <v>-25676000</v>
+        <v>12558000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-25676000</v>
+        <v>12558000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-25676000</v>
+        <v>12558000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-25676000</v>
+        <v>12558000</v>
       </c>
       <c r="AB3" t="n">
-        <v>6026000</v>
+        <v>6218000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-19650000</v>
+        <v>18776000</v>
       </c>
       <c r="AD3" t="n">
-        <v>3113000</v>
+        <v>3913000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-8065000</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
+        <v>-1355000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-179000</v>
+      </c>
       <c r="AG3" t="n">
-        <v>3089000</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>4615000</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-2512000</v>
+        <v>-1732000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3164000</v>
+        <v>2203000</v>
       </c>
       <c r="AK3" t="n">
-        <v>652000</v>
+        <v>471000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-11795000</v>
+        <v>17752000</v>
       </c>
       <c r="AM3" t="n">
-        <v>174348000</v>
+        <v>155704000</v>
       </c>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>180574000</v>
+        <v>166859000</v>
       </c>
       <c r="AP3" t="n">
-        <v>59524000</v>
+        <v>53435000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>121050000</v>
+        <v>113424000</v>
       </c>
       <c r="AR3" t="n">
-        <v>162553000</v>
+        <v>173456000</v>
       </c>
       <c r="AS3" t="n">
-        <v>209757000</v>
+        <v>235116000</v>
       </c>
       <c r="AT3" t="n">
-        <v>372310000</v>
+        <v>408572000</v>
       </c>
       <c r="AU3" t="n">
-        <v>372310000</v>
+        <v>408572000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-382967</v>
+        <v>-1982000</v>
       </c>
       <c r="C4" t="n">
-        <v>0.331</v>
+        <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>48299000</v>
+        <v>22358000</v>
       </c>
       <c r="E4" t="n">
-        <v>377000</v>
+        <v>-7567000</v>
       </c>
       <c r="F4" t="n">
-        <v>-1157000</v>
+        <v>-7928000</v>
       </c>
       <c r="G4" t="n">
-        <v>12558000</v>
+        <v>-25676000</v>
       </c>
       <c r="H4" t="n">
-        <v>27697000</v>
+        <v>31277000</v>
       </c>
       <c r="I4" t="n">
-        <v>235116000</v>
+        <v>209757000</v>
       </c>
       <c r="J4" t="n">
-        <v>48676000</v>
+        <v>14791000</v>
       </c>
       <c r="K4" t="n">
-        <v>20979000</v>
+        <v>-16486000</v>
       </c>
       <c r="L4" t="n">
-        <v>-1732000</v>
+        <v>-2512000</v>
       </c>
       <c r="M4" t="n">
-        <v>2203000</v>
+        <v>3164000</v>
       </c>
       <c r="N4" t="n">
-        <v>471000</v>
+        <v>652000</v>
       </c>
       <c r="O4" t="n">
-        <v>14866033</v>
+        <v>-19369000</v>
       </c>
       <c r="P4" t="n">
-        <v>12558000</v>
+        <v>-25676000</v>
       </c>
       <c r="Q4" t="n">
-        <v>390820000</v>
+        <v>384105000</v>
       </c>
       <c r="R4" t="n">
         <v>2000000000</v>
@@ -994,223 +992,225 @@
         <v>2000000000</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0063</v>
+        <v>-0.0128</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0063</v>
+        <v>-0.0128</v>
       </c>
       <c r="V4" t="n">
-        <v>12558000</v>
+        <v>-25676000</v>
       </c>
       <c r="W4" t="n">
-        <v>12558000</v>
+        <v>-25676000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>12558000</v>
+        <v>-25676000</v>
       </c>
       <c r="Z4" t="n">
-        <v>12558000</v>
+        <v>-25676000</v>
       </c>
       <c r="AA4" t="n">
-        <v>12558000</v>
+        <v>-25676000</v>
       </c>
       <c r="AB4" t="n">
-        <v>6218000</v>
+        <v>6026000</v>
       </c>
       <c r="AC4" t="n">
-        <v>18776000</v>
+        <v>-19650000</v>
       </c>
       <c r="AD4" t="n">
-        <v>3913000</v>
+        <v>3113000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-1355000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-179000</v>
-      </c>
+        <v>-8065000</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>3089000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>4615000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1732000</v>
+        <v>-2512000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2203000</v>
+        <v>3164000</v>
       </c>
       <c r="AK4" t="n">
-        <v>471000</v>
+        <v>652000</v>
       </c>
       <c r="AL4" t="n">
-        <v>17752000</v>
+        <v>-11795000</v>
       </c>
       <c r="AM4" t="n">
-        <v>155704000</v>
+        <v>174348000</v>
       </c>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>166859000</v>
+        <v>180574000</v>
       </c>
       <c r="AP4" t="n">
-        <v>53435000</v>
+        <v>59524000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>113424000</v>
+        <v>121050000</v>
       </c>
       <c r="AR4" t="n">
-        <v>173456000</v>
+        <v>162553000</v>
       </c>
       <c r="AS4" t="n">
-        <v>235116000</v>
+        <v>209757000</v>
       </c>
       <c r="AT4" t="n">
-        <v>408572000</v>
+        <v>372310000</v>
       </c>
       <c r="AU4" t="n">
-        <v>408572000</v>
+        <v>372310000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>201190</v>
+        <v>21844</v>
       </c>
       <c r="C5" t="n">
-        <v>0.295</v>
+        <v>0.172</v>
       </c>
       <c r="D5" t="n">
-        <v>49894000</v>
+        <v>110805000</v>
       </c>
       <c r="E5" t="n">
-        <v>682000</v>
+        <v>127000</v>
       </c>
       <c r="F5" t="n">
-        <v>682000</v>
+        <v>127000</v>
       </c>
       <c r="G5" t="n">
-        <v>14984000</v>
+        <v>61859000</v>
       </c>
       <c r="H5" t="n">
-        <v>27069000</v>
+        <v>33821000</v>
       </c>
       <c r="I5" t="n">
-        <v>204503000</v>
+        <v>280430000</v>
       </c>
       <c r="J5" t="n">
-        <v>50576000</v>
+        <v>110932000</v>
       </c>
       <c r="K5" t="n">
-        <v>23507000</v>
+        <v>77111000</v>
       </c>
       <c r="L5" t="n">
-        <v>-1989000</v>
+        <v>-1922000</v>
       </c>
       <c r="M5" t="n">
-        <v>2253000</v>
+        <v>2364000</v>
       </c>
       <c r="N5" t="n">
-        <v>264000</v>
+        <v>442000</v>
       </c>
       <c r="O5" t="n">
-        <v>14503190</v>
+        <v>61753844</v>
       </c>
       <c r="P5" t="n">
-        <v>14984000</v>
+        <v>61859000</v>
       </c>
       <c r="Q5" t="n">
-        <v>342907000</v>
+        <v>477617000</v>
       </c>
       <c r="R5" t="n">
-        <v>2000000000</v>
+        <v>1995453825</v>
       </c>
       <c r="S5" t="n">
-        <v>2000000000</v>
+        <v>1995453825</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0075</v>
+        <v>0.031</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0075</v>
+        <v>0.031</v>
       </c>
       <c r="V5" t="n">
-        <v>14984000</v>
+        <v>61859000</v>
       </c>
       <c r="W5" t="n">
-        <v>14984000</v>
+        <v>61859000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>14984000</v>
+        <v>61859000</v>
       </c>
       <c r="Z5" t="n">
-        <v>14984000</v>
+        <v>61859000</v>
       </c>
       <c r="AA5" t="n">
-        <v>14984000</v>
+        <v>61859000</v>
       </c>
       <c r="AB5" t="n">
-        <v>6270000</v>
+        <v>12888000</v>
       </c>
       <c r="AC5" t="n">
-        <v>21254000</v>
+        <v>74747000</v>
       </c>
       <c r="AD5" t="n">
-        <v>2955000</v>
+        <v>3002000</v>
       </c>
       <c r="AE5" t="n">
-        <v>487000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-487000</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
       <c r="AI5" t="n">
-        <v>-1989000</v>
+        <v>-1922000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2253000</v>
+        <v>2364000</v>
       </c>
       <c r="AK5" t="n">
-        <v>264000</v>
+        <v>442000</v>
       </c>
       <c r="AL5" t="n">
-        <v>19606000</v>
+        <v>73432000</v>
       </c>
       <c r="AM5" t="n">
-        <v>138404000</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
+        <v>197187000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>2433000</v>
+      </c>
       <c r="AO5" t="n">
-        <v>140933000</v>
+        <v>196881000</v>
       </c>
       <c r="AP5" t="n">
-        <v>45790000</v>
+        <v>61243000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>95143000</v>
+        <v>135638000</v>
       </c>
       <c r="AR5" t="n">
-        <v>158010000</v>
+        <v>270619000</v>
       </c>
       <c r="AS5" t="n">
-        <v>204503000</v>
+        <v>280430000</v>
       </c>
       <c r="AT5" t="n">
-        <v>362513000</v>
+        <v>551049000</v>
       </c>
       <c r="AU5" t="n">
-        <v>362513000</v>
+        <v>551049000</v>
       </c>
     </row>
   </sheetData>
@@ -1581,55 +1581,51 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>10410000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1989590000</v>
+        <v>2000000000</v>
       </c>
       <c r="D2" t="n">
         <v>2000000000</v>
       </c>
       <c r="E2" t="n">
-        <v>67672000</v>
+        <v>46148000</v>
       </c>
       <c r="F2" t="n">
-        <v>245365000</v>
+        <v>247157000</v>
       </c>
       <c r="G2" t="n">
-        <v>252180000</v>
+        <v>263288000</v>
       </c>
       <c r="H2" t="n">
-        <v>88066000</v>
+        <v>107782000</v>
       </c>
       <c r="I2" t="n">
-        <v>245365000</v>
+        <v>247157000</v>
       </c>
       <c r="J2" t="n">
-        <v>61426000</v>
+        <v>32526000</v>
       </c>
       <c r="K2" t="n">
-        <v>245934000</v>
+        <v>249666000</v>
       </c>
       <c r="L2" t="n">
-        <v>245934000</v>
+        <v>249666000</v>
       </c>
       <c r="M2" t="n">
-        <v>245934000</v>
+        <v>249666000</v>
       </c>
       <c r="N2" t="n">
-        <v>245934000</v>
+        <v>249666000</v>
       </c>
       <c r="O2" t="n">
-        <v>50000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>416000</v>
-      </c>
+        <v>35000</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>186418000</v>
+        <v>146677000</v>
       </c>
       <c r="R2" t="n">
         <v>277051000</v>
@@ -1641,154 +1637,156 @@
         <v>20000000</v>
       </c>
       <c r="U2" t="n">
-        <v>206496000</v>
+        <v>151362000</v>
       </c>
       <c r="V2" t="n">
-        <v>53996000</v>
+        <v>22774000</v>
       </c>
       <c r="W2" t="n">
-        <v>160000</v>
+        <v>626000</v>
       </c>
       <c r="X2" t="n">
-        <v>1990000</v>
+        <v>1039000</v>
       </c>
       <c r="Y2" t="n">
-        <v>51846000</v>
+        <v>21109000</v>
       </c>
       <c r="Z2" t="n">
-        <v>51846000</v>
+        <v>21109000</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>152500000</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>128588000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>626000</v>
+      </c>
       <c r="AD2" t="n">
-        <v>15826000</v>
+        <v>25039000</v>
       </c>
       <c r="AE2" t="n">
-        <v>9580000</v>
+        <v>11417000</v>
       </c>
       <c r="AF2" t="n">
-        <v>6246000</v>
+        <v>13622000</v>
       </c>
       <c r="AG2" t="n">
-        <v>106143000</v>
+        <v>103549000</v>
       </c>
       <c r="AH2" t="n">
-        <v>25487000</v>
+        <v>39932000</v>
       </c>
       <c r="AI2" t="n">
-        <v>16423000</v>
+        <v>7854000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>64233000</v>
+        <v>55763000</v>
       </c>
       <c r="AK2" t="n">
-        <v>452430000</v>
+        <v>401028000</v>
       </c>
       <c r="AL2" t="n">
-        <v>211864000</v>
+        <v>164658000</v>
       </c>
       <c r="AM2" t="n">
-        <v>3687000</v>
+        <v>4766000</v>
       </c>
       <c r="AN2" t="n">
-        <v>476000</v>
+        <v>407000</v>
       </c>
       <c r="AO2" t="n">
-        <v>6067000</v>
+        <v>5599000</v>
       </c>
       <c r="AP2" t="n">
-        <v>6067000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>5789000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>5789000</v>
-      </c>
+        <v>5599000</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
-        <v>569000</v>
+        <v>2509000</v>
       </c>
       <c r="AT2" t="n">
-        <v>569000</v>
+        <v>977000</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1532000</v>
       </c>
       <c r="AV2" t="n">
-        <v>195276000</v>
+        <v>151377000</v>
       </c>
       <c r="AW2" t="n">
-        <v>-175119000</v>
+        <v>-159546000</v>
       </c>
       <c r="AX2" t="n">
-        <v>370395000</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+        <v>310923000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>14249000</v>
+      </c>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
-        <v>258584000</v>
+        <v>249548000</v>
       </c>
       <c r="BB2" t="n">
-        <v>111811000</v>
+        <v>47126000</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>240566000</v>
+        <v>236370000</v>
       </c>
       <c r="BE2" t="n">
-        <v>4306000</v>
-      </c>
-      <c r="BF2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>15385000</v>
+      </c>
       <c r="BG2" t="n">
-        <v>83227000</v>
+        <v>65112000</v>
       </c>
       <c r="BH2" t="n">
-        <v>27482000</v>
+        <v>29622000</v>
       </c>
       <c r="BI2" t="n">
-        <v>19377000</v>
+        <v>17215000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>36368000</v>
+        <v>18275000</v>
       </c>
       <c r="BK2" t="n">
-        <v>26882000</v>
+        <v>15385000</v>
       </c>
       <c r="BL2" t="n">
-        <v>70000</v>
+        <v>80000</v>
       </c>
       <c r="BM2" t="n">
-        <v>57562000</v>
+        <v>53692000</v>
       </c>
       <c r="BN2" t="n">
-        <v>-2572000</v>
+        <v>-203000</v>
       </c>
       <c r="BO2" t="n">
-        <v>60134000</v>
+        <v>53895000</v>
       </c>
       <c r="BP2" t="n">
-        <v>68519000</v>
+        <v>102101000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>68519000</v>
+        <v>102101000</v>
       </c>
       <c r="BR2" t="n">
-        <v>8567000</v>
+        <v>59418000</v>
       </c>
       <c r="BS2" t="n">
-        <v>59952000</v>
+        <v>42683000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
@@ -1798,41 +1796,41 @@
         <v>2000000000</v>
       </c>
       <c r="E3" t="n">
-        <v>48180000</v>
+        <v>51070000</v>
       </c>
       <c r="F3" t="n">
-        <v>194357000</v>
+        <v>232844000</v>
       </c>
       <c r="G3" t="n">
-        <v>218147000</v>
+        <v>260142000</v>
       </c>
       <c r="H3" t="n">
-        <v>28598000</v>
+        <v>70376000</v>
       </c>
       <c r="I3" t="n">
-        <v>194357000</v>
+        <v>232844000</v>
       </c>
       <c r="J3" t="n">
-        <v>25065000</v>
+        <v>30188000</v>
       </c>
       <c r="K3" t="n">
-        <v>195032000</v>
+        <v>239260000</v>
       </c>
       <c r="L3" t="n">
-        <v>196363000</v>
+        <v>242277000</v>
       </c>
       <c r="M3" t="n">
-        <v>195032000</v>
+        <v>239260000</v>
       </c>
       <c r="N3" t="n">
-        <v>195032000</v>
+        <v>239260000</v>
       </c>
       <c r="O3" t="n">
-        <v>50000</v>
+        <v>42000</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>124559000</v>
+        <v>154235000</v>
       </c>
       <c r="R3" t="n">
         <v>277051000</v>
@@ -1844,156 +1842,160 @@
         <v>20000000</v>
       </c>
       <c r="U3" t="n">
-        <v>174393000</v>
+        <v>155807000</v>
       </c>
       <c r="V3" t="n">
-        <v>21234000</v>
+        <v>20286000</v>
       </c>
       <c r="W3" t="n">
-        <v>3417000</v>
+        <v>442000</v>
       </c>
       <c r="X3" t="n">
-        <v>1822000</v>
+        <v>1618000</v>
       </c>
       <c r="Y3" t="n">
-        <v>15995000</v>
+        <v>18226000</v>
       </c>
       <c r="Z3" t="n">
-        <v>14664000</v>
+        <v>15209000</v>
       </c>
       <c r="AA3" t="n">
-        <v>1331000</v>
+        <v>3017000</v>
       </c>
       <c r="AB3" t="n">
-        <v>153159000</v>
+        <v>135521000</v>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>32185000</v>
+        <v>32844000</v>
       </c>
       <c r="AE3" t="n">
-        <v>10401000</v>
+        <v>14979000</v>
       </c>
       <c r="AF3" t="n">
-        <v>21784000</v>
+        <v>17865000</v>
       </c>
       <c r="AG3" t="n">
-        <v>88141000</v>
+        <v>102677000</v>
       </c>
       <c r="AH3" t="n">
-        <v>18334000</v>
+        <v>40808000</v>
       </c>
       <c r="AI3" t="n">
-        <v>12484000</v>
+        <v>8297000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>57323000</v>
+        <v>53572000</v>
       </c>
       <c r="AK3" t="n">
-        <v>369425000</v>
+        <v>395067000</v>
       </c>
       <c r="AL3" t="n">
-        <v>187668000</v>
+        <v>189170000</v>
       </c>
       <c r="AM3" t="n">
-        <v>2671000</v>
+        <v>9556000</v>
       </c>
       <c r="AN3" t="n">
-        <v>506000</v>
+        <v>504000</v>
       </c>
       <c r="AO3" t="n">
-        <v>5940000</v>
+        <v>5803000</v>
       </c>
       <c r="AP3" t="n">
-        <v>5940000</v>
+        <v>5803000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5681000</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>5681000</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>675000</v>
+        <v>6416000</v>
       </c>
       <c r="AT3" t="n">
-        <v>675000</v>
+        <v>6055000</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>361000</v>
       </c>
       <c r="AV3" t="n">
-        <v>172195000</v>
+        <v>166891000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-166602000</v>
+        <v>-161840000</v>
       </c>
       <c r="AX3" t="n">
-        <v>338797000</v>
+        <v>328731000</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="inlineStr"/>
+        <v>29956000</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>166891000</v>
+      </c>
       <c r="BA3" t="n">
-        <v>260674000</v>
+        <v>250954000</v>
       </c>
       <c r="BB3" t="n">
-        <v>78123000</v>
+        <v>47821000</v>
       </c>
       <c r="BC3" t="n">
         <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>181757000</v>
+        <v>205897000</v>
       </c>
       <c r="BE3" t="n">
-        <v>14575000</v>
-      </c>
-      <c r="BF3" t="inlineStr"/>
+        <v>14138000</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>16982000</v>
+      </c>
       <c r="BG3" t="n">
-        <v>70163000</v>
+        <v>68758000</v>
       </c>
       <c r="BH3" t="n">
-        <v>21906000</v>
+        <v>25568000</v>
       </c>
       <c r="BI3" t="n">
-        <v>23386000</v>
+        <v>15214000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>24871000</v>
+        <v>27976000</v>
       </c>
       <c r="BK3" t="n">
-        <v>17877000</v>
+        <v>16982000</v>
       </c>
       <c r="BL3" t="n">
-        <v>72000</v>
+        <v>771000</v>
       </c>
       <c r="BM3" t="n">
-        <v>44912000</v>
+        <v>42923000</v>
       </c>
       <c r="BN3" t="n">
-        <v>-654000</v>
+        <v>-854000</v>
       </c>
       <c r="BO3" t="n">
-        <v>45566000</v>
+        <v>43777000</v>
       </c>
       <c r="BP3" t="n">
-        <v>34158000</v>
+        <v>62325000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>34158000</v>
+        <v>62325000</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>10034000</v>
       </c>
       <c r="BS3" t="n">
-        <v>34158000</v>
+        <v>52291000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
@@ -2003,41 +2005,41 @@
         <v>2000000000</v>
       </c>
       <c r="E4" t="n">
-        <v>51070000</v>
+        <v>48180000</v>
       </c>
       <c r="F4" t="n">
-        <v>232844000</v>
+        <v>194357000</v>
       </c>
       <c r="G4" t="n">
-        <v>260142000</v>
+        <v>218147000</v>
       </c>
       <c r="H4" t="n">
-        <v>70376000</v>
+        <v>28598000</v>
       </c>
       <c r="I4" t="n">
-        <v>232844000</v>
+        <v>194357000</v>
       </c>
       <c r="J4" t="n">
-        <v>30188000</v>
+        <v>25065000</v>
       </c>
       <c r="K4" t="n">
-        <v>239260000</v>
+        <v>195032000</v>
       </c>
       <c r="L4" t="n">
-        <v>242277000</v>
+        <v>196363000</v>
       </c>
       <c r="M4" t="n">
-        <v>239260000</v>
+        <v>195032000</v>
       </c>
       <c r="N4" t="n">
-        <v>239260000</v>
+        <v>195032000</v>
       </c>
       <c r="O4" t="n">
-        <v>42000</v>
+        <v>50000</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>154235000</v>
+        <v>124559000</v>
       </c>
       <c r="R4" t="n">
         <v>277051000</v>
@@ -2049,204 +2051,204 @@
         <v>20000000</v>
       </c>
       <c r="U4" t="n">
-        <v>155807000</v>
+        <v>174393000</v>
       </c>
       <c r="V4" t="n">
-        <v>20286000</v>
+        <v>21234000</v>
       </c>
       <c r="W4" t="n">
-        <v>442000</v>
+        <v>3417000</v>
       </c>
       <c r="X4" t="n">
-        <v>1618000</v>
+        <v>1822000</v>
       </c>
       <c r="Y4" t="n">
-        <v>18226000</v>
+        <v>15995000</v>
       </c>
       <c r="Z4" t="n">
-        <v>15209000</v>
+        <v>14664000</v>
       </c>
       <c r="AA4" t="n">
-        <v>3017000</v>
+        <v>1331000</v>
       </c>
       <c r="AB4" t="n">
-        <v>135521000</v>
+        <v>153159000</v>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>32844000</v>
+        <v>32185000</v>
       </c>
       <c r="AE4" t="n">
-        <v>14979000</v>
+        <v>10401000</v>
       </c>
       <c r="AF4" t="n">
-        <v>17865000</v>
+        <v>21784000</v>
       </c>
       <c r="AG4" t="n">
-        <v>102677000</v>
+        <v>88141000</v>
       </c>
       <c r="AH4" t="n">
-        <v>40808000</v>
+        <v>18334000</v>
       </c>
       <c r="AI4" t="n">
-        <v>8297000</v>
+        <v>12484000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>53572000</v>
+        <v>57323000</v>
       </c>
       <c r="AK4" t="n">
-        <v>395067000</v>
+        <v>369425000</v>
       </c>
       <c r="AL4" t="n">
-        <v>189170000</v>
+        <v>187668000</v>
       </c>
       <c r="AM4" t="n">
-        <v>9556000</v>
+        <v>2671000</v>
       </c>
       <c r="AN4" t="n">
-        <v>504000</v>
+        <v>506000</v>
       </c>
       <c r="AO4" t="n">
-        <v>5803000</v>
+        <v>5940000</v>
       </c>
       <c r="AP4" t="n">
-        <v>5803000</v>
+        <v>5940000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>5681000</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>5681000</v>
       </c>
       <c r="AS4" t="n">
-        <v>6416000</v>
+        <v>675000</v>
       </c>
       <c r="AT4" t="n">
-        <v>6055000</v>
+        <v>675000</v>
       </c>
       <c r="AU4" t="n">
-        <v>361000</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>166891000</v>
+        <v>172195000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-161840000</v>
+        <v>-166602000</v>
       </c>
       <c r="AX4" t="n">
-        <v>328731000</v>
+        <v>338797000</v>
       </c>
       <c r="AY4" t="n">
-        <v>29956000</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>166891000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>250954000</v>
+        <v>260674000</v>
       </c>
       <c r="BB4" t="n">
-        <v>47821000</v>
+        <v>78123000</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>205897000</v>
+        <v>181757000</v>
       </c>
       <c r="BE4" t="n">
-        <v>14138000</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>16982000</v>
-      </c>
+        <v>14575000</v>
+      </c>
+      <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="n">
-        <v>68758000</v>
+        <v>70163000</v>
       </c>
       <c r="BH4" t="n">
-        <v>25568000</v>
+        <v>21906000</v>
       </c>
       <c r="BI4" t="n">
-        <v>15214000</v>
+        <v>23386000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>27976000</v>
+        <v>24871000</v>
       </c>
       <c r="BK4" t="n">
-        <v>16982000</v>
+        <v>17877000</v>
       </c>
       <c r="BL4" t="n">
-        <v>771000</v>
+        <v>72000</v>
       </c>
       <c r="BM4" t="n">
-        <v>42923000</v>
+        <v>44912000</v>
       </c>
       <c r="BN4" t="n">
-        <v>-854000</v>
+        <v>-654000</v>
       </c>
       <c r="BO4" t="n">
-        <v>43777000</v>
+        <v>45566000</v>
       </c>
       <c r="BP4" t="n">
-        <v>62325000</v>
+        <v>34158000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>62325000</v>
+        <v>34158000</v>
       </c>
       <c r="BR4" t="n">
-        <v>10034000</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>52291000</v>
+        <v>34158000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B5" t="inlineStr"/>
+        <v>45657</v>
+      </c>
+      <c r="B5" t="n">
+        <v>10410000</v>
+      </c>
       <c r="C5" t="n">
-        <v>2000000000</v>
+        <v>1989590000</v>
       </c>
       <c r="D5" t="n">
         <v>2000000000</v>
       </c>
       <c r="E5" t="n">
-        <v>46148000</v>
+        <v>67672000</v>
       </c>
       <c r="F5" t="n">
-        <v>247157000</v>
+        <v>245365000</v>
       </c>
       <c r="G5" t="n">
-        <v>263288000</v>
+        <v>252180000</v>
       </c>
       <c r="H5" t="n">
-        <v>107782000</v>
+        <v>88066000</v>
       </c>
       <c r="I5" t="n">
-        <v>247157000</v>
+        <v>245365000</v>
       </c>
       <c r="J5" t="n">
-        <v>32526000</v>
+        <v>61426000</v>
       </c>
       <c r="K5" t="n">
-        <v>249666000</v>
+        <v>245934000</v>
       </c>
       <c r="L5" t="n">
-        <v>249666000</v>
+        <v>245934000</v>
       </c>
       <c r="M5" t="n">
-        <v>249666000</v>
+        <v>245934000</v>
       </c>
       <c r="N5" t="n">
-        <v>249666000</v>
+        <v>245934000</v>
       </c>
       <c r="O5" t="n">
-        <v>35000</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
+        <v>50000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>416000</v>
+      </c>
       <c r="Q5" t="n">
-        <v>146677000</v>
+        <v>186418000</v>
       </c>
       <c r="R5" t="n">
         <v>277051000</v>
@@ -2258,151 +2260,149 @@
         <v>20000000</v>
       </c>
       <c r="U5" t="n">
-        <v>151362000</v>
+        <v>206496000</v>
       </c>
       <c r="V5" t="n">
-        <v>22774000</v>
+        <v>53996000</v>
       </c>
       <c r="W5" t="n">
-        <v>626000</v>
+        <v>160000</v>
       </c>
       <c r="X5" t="n">
-        <v>1039000</v>
+        <v>1990000</v>
       </c>
       <c r="Y5" t="n">
-        <v>21109000</v>
+        <v>51846000</v>
       </c>
       <c r="Z5" t="n">
-        <v>21109000</v>
+        <v>51846000</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>128588000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>626000</v>
-      </c>
+        <v>152500000</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>25039000</v>
+        <v>15826000</v>
       </c>
       <c r="AE5" t="n">
-        <v>11417000</v>
+        <v>9580000</v>
       </c>
       <c r="AF5" t="n">
-        <v>13622000</v>
+        <v>6246000</v>
       </c>
       <c r="AG5" t="n">
-        <v>103549000</v>
+        <v>106143000</v>
       </c>
       <c r="AH5" t="n">
-        <v>39932000</v>
+        <v>25487000</v>
       </c>
       <c r="AI5" t="n">
-        <v>7854000</v>
+        <v>16423000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>55763000</v>
+        <v>64233000</v>
       </c>
       <c r="AK5" t="n">
-        <v>401028000</v>
+        <v>452430000</v>
       </c>
       <c r="AL5" t="n">
-        <v>164658000</v>
+        <v>211864000</v>
       </c>
       <c r="AM5" t="n">
-        <v>4766000</v>
+        <v>3687000</v>
       </c>
       <c r="AN5" t="n">
-        <v>407000</v>
+        <v>476000</v>
       </c>
       <c r="AO5" t="n">
-        <v>5599000</v>
+        <v>6067000</v>
       </c>
       <c r="AP5" t="n">
-        <v>5599000</v>
-      </c>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
+        <v>6067000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5789000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>5789000</v>
+      </c>
       <c r="AS5" t="n">
-        <v>2509000</v>
+        <v>569000</v>
       </c>
       <c r="AT5" t="n">
-        <v>977000</v>
+        <v>569000</v>
       </c>
       <c r="AU5" t="n">
-        <v>1532000</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>151377000</v>
+        <v>195276000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-159546000</v>
+        <v>-175119000</v>
       </c>
       <c r="AX5" t="n">
-        <v>310923000</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>14249000</v>
-      </c>
+        <v>370395000</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
-        <v>249548000</v>
+        <v>258584000</v>
       </c>
       <c r="BB5" t="n">
-        <v>47126000</v>
+        <v>111811000</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>236370000</v>
+        <v>240566000</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>15385000</v>
-      </c>
+        <v>4306000</v>
+      </c>
+      <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="n">
-        <v>65112000</v>
+        <v>83227000</v>
       </c>
       <c r="BH5" t="n">
-        <v>29622000</v>
+        <v>27482000</v>
       </c>
       <c r="BI5" t="n">
-        <v>17215000</v>
+        <v>19377000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>18275000</v>
+        <v>36368000</v>
       </c>
       <c r="BK5" t="n">
-        <v>15385000</v>
+        <v>26882000</v>
       </c>
       <c r="BL5" t="n">
-        <v>80000</v>
+        <v>70000</v>
       </c>
       <c r="BM5" t="n">
-        <v>53692000</v>
+        <v>57562000</v>
       </c>
       <c r="BN5" t="n">
-        <v>-203000</v>
+        <v>-2572000</v>
       </c>
       <c r="BO5" t="n">
-        <v>53895000</v>
+        <v>60134000</v>
       </c>
       <c r="BP5" t="n">
-        <v>102101000</v>
+        <v>68519000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>102101000</v>
+        <v>68519000</v>
       </c>
       <c r="BR5" t="n">
-        <v>59418000</v>
+        <v>8567000</v>
       </c>
       <c r="BS5" t="n">
-        <v>42683000</v>
+        <v>59952000</v>
       </c>
     </row>
   </sheetData>
@@ -2668,572 +2668,572 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>59638000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-416000</v>
-      </c>
+        <v>8357000</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>-15650000</v>
+        <v>-7541000</v>
       </c>
       <c r="E2" t="n">
-        <v>2939000</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
       <c r="G2" t="n">
-        <v>-21922000</v>
+        <v>-36186000</v>
       </c>
       <c r="H2" t="n">
-        <v>72825000</v>
+        <v>102101000</v>
       </c>
       <c r="I2" t="n">
-        <v>34221000</v>
+        <v>114743000</v>
       </c>
       <c r="J2" t="n">
-        <v>-1653000</v>
+        <v>-129000</v>
       </c>
       <c r="K2" t="n">
-        <v>40257000</v>
+        <v>-12513000</v>
       </c>
       <c r="L2" t="n">
-        <v>-27930000</v>
+        <v>-21685000</v>
       </c>
       <c r="M2" t="n">
-        <v>-2364000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>-2253000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-1500000</v>
+      </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>-1500000</v>
       </c>
       <c r="P2" t="n">
-        <v>-416000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-416000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
       <c r="S2" t="n">
-        <v>-12711000</v>
+        <v>-7541000</v>
       </c>
       <c r="T2" t="n">
-        <v>-12711000</v>
+        <v>-7541000</v>
       </c>
       <c r="U2" t="n">
-        <v>-15650000</v>
+        <v>-7541000</v>
       </c>
       <c r="V2" t="n">
-        <v>2939000</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-13373000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>10421000</v>
-      </c>
+        <v>-35371000</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>442000</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
+        <v>264000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
       <c r="AB2" t="n">
-        <v>-3119000</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-3119000</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-732000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-732000</v>
+      </c>
       <c r="AF2" t="n">
-        <v>-21117000</v>
+        <v>-34903000</v>
       </c>
       <c r="AG2" t="n">
-        <v>805000</v>
+        <v>551000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-21922000</v>
+        <v>-35454000</v>
       </c>
       <c r="AI2" t="n">
-        <v>81560000</v>
+        <v>44543000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-7917000</v>
+        <v>-1432000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-25697000</v>
+        <v>-4368000</v>
       </c>
       <c r="AL2" t="n">
-        <v>20191000</v>
+        <v>31780000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-9814000</v>
+        <v>-5173000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-19394000</v>
+        <v>-13845000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-16680000</v>
+        <v>-17130000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1789000</v>
+        <v>1540000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="AR2" t="n">
-        <v>3248000</v>
+        <v>782000</v>
       </c>
       <c r="AS2" t="n">
-        <v>33821000</v>
+        <v>27069000</v>
       </c>
       <c r="AT2" t="n">
-        <v>89000</v>
+        <v>38000</v>
       </c>
       <c r="AU2" t="n">
-        <v>33732000</v>
+        <v>27031000</v>
       </c>
       <c r="AV2" t="n">
-        <v>-127000</v>
+        <v>-195000</v>
       </c>
       <c r="AW2" t="n">
-        <v>-177000</v>
+        <v>-183000</v>
       </c>
       <c r="AX2" t="n">
-        <v>74747000</v>
+        <v>21254000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-10860000</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
+        <v>-4808000</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>-19721000</v>
+        <v>-8841000</v>
       </c>
       <c r="E3" t="n">
-        <v>17863000</v>
+        <v>13000000</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>-32112000</v>
+        <v>-53060000</v>
       </c>
       <c r="H3" t="n">
-        <v>34221000</v>
+        <v>66346000</v>
       </c>
       <c r="I3" t="n">
-        <v>66346000</v>
+        <v>102101000</v>
       </c>
       <c r="J3" t="n">
-        <v>-1197000</v>
+        <v>-1593000</v>
       </c>
       <c r="K3" t="n">
-        <v>-30928000</v>
+        <v>-34162000</v>
       </c>
       <c r="L3" t="n">
-        <v>-21048000</v>
+        <v>-13935000</v>
       </c>
       <c r="M3" t="n">
-        <v>-3164000</v>
+        <v>-2203000</v>
       </c>
       <c r="N3" t="n">
-        <v>-4000000</v>
+        <v>-5000000</v>
       </c>
       <c r="O3" t="n">
-        <v>-4000000</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
+        <v>-5000000</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>-1858000</v>
+        <v>4159000</v>
       </c>
       <c r="T3" t="n">
-        <v>-1858000</v>
+        <v>4159000</v>
       </c>
       <c r="U3" t="n">
-        <v>-19721000</v>
+        <v>-8841000</v>
       </c>
       <c r="V3" t="n">
-        <v>17863000</v>
+        <v>13000000</v>
       </c>
       <c r="W3" t="n">
-        <v>-31132000</v>
+        <v>-68479000</v>
       </c>
       <c r="X3" t="n">
-        <v>-304000</v>
+        <v>-10117000</v>
       </c>
       <c r="Y3" t="n">
-        <v>652000</v>
+        <v>471000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-3061000</v>
+        <v>-5890000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-3061000</v>
-      </c>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+        <v>-5890000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
       <c r="AF3" t="n">
-        <v>-28419000</v>
+        <v>-53028000</v>
       </c>
       <c r="AG3" t="n">
-        <v>3693000</v>
+        <v>32000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-32112000</v>
+        <v>-53060000</v>
       </c>
       <c r="AI3" t="n">
-        <v>21252000</v>
+        <v>48252000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-508000</v>
+        <v>-5226000</v>
       </c>
       <c r="AK3" t="n">
-        <v>385000</v>
+        <v>3854000</v>
       </c>
       <c r="AL3" t="n">
-        <v>13358000</v>
+        <v>3712000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-3094000</v>
+        <v>1503000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-5135000</v>
+        <v>-9391000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-4744000</v>
+        <v>8030000</v>
       </c>
       <c r="AP3" t="n">
-        <v>2378000</v>
+        <v>1413000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1135000</v>
+        <v>-433000</v>
       </c>
       <c r="AS3" t="n">
-        <v>31277000</v>
+        <v>27697000</v>
       </c>
       <c r="AT3" t="n">
-        <v>752000</v>
+        <v>345000</v>
       </c>
       <c r="AU3" t="n">
-        <v>30525000</v>
+        <v>27352000</v>
       </c>
       <c r="AV3" t="n">
-        <v>-137000</v>
+        <v>-198000</v>
       </c>
       <c r="AW3" t="n">
-        <v>217000</v>
+        <v>154000</v>
       </c>
       <c r="AX3" t="n">
-        <v>-19650000</v>
+        <v>18776000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-4808000</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>-10860000</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
       <c r="D4" t="n">
-        <v>-8841000</v>
+        <v>-19721000</v>
       </c>
       <c r="E4" t="n">
-        <v>13000000</v>
+        <v>17863000</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>-53060000</v>
+        <v>-32112000</v>
       </c>
       <c r="H4" t="n">
+        <v>34221000</v>
+      </c>
+      <c r="I4" t="n">
         <v>66346000</v>
       </c>
-      <c r="I4" t="n">
-        <v>102101000</v>
-      </c>
       <c r="J4" t="n">
-        <v>-1593000</v>
+        <v>-1197000</v>
       </c>
       <c r="K4" t="n">
-        <v>-34162000</v>
+        <v>-30928000</v>
       </c>
       <c r="L4" t="n">
-        <v>-13935000</v>
+        <v>-21048000</v>
       </c>
       <c r="M4" t="n">
-        <v>-2203000</v>
+        <v>-3164000</v>
       </c>
       <c r="N4" t="n">
-        <v>-5000000</v>
+        <v>-4000000</v>
       </c>
       <c r="O4" t="n">
-        <v>-5000000</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+        <v>-4000000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>4159000</v>
+        <v>-1858000</v>
       </c>
       <c r="T4" t="n">
-        <v>4159000</v>
+        <v>-1858000</v>
       </c>
       <c r="U4" t="n">
-        <v>-8841000</v>
+        <v>-19721000</v>
       </c>
       <c r="V4" t="n">
-        <v>13000000</v>
+        <v>17863000</v>
       </c>
       <c r="W4" t="n">
-        <v>-68479000</v>
+        <v>-31132000</v>
       </c>
       <c r="X4" t="n">
-        <v>-10117000</v>
+        <v>-304000</v>
       </c>
       <c r="Y4" t="n">
-        <v>471000</v>
+        <v>652000</v>
       </c>
       <c r="Z4" t="n">
-        <v>85000</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>85000</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-5890000</v>
+        <v>-3061000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-5890000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
+        <v>-3061000</v>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>-53028000</v>
+        <v>-28419000</v>
       </c>
       <c r="AG4" t="n">
-        <v>32000</v>
+        <v>3693000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-53060000</v>
+        <v>-32112000</v>
       </c>
       <c r="AI4" t="n">
-        <v>48252000</v>
+        <v>21252000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-5226000</v>
+        <v>-508000</v>
       </c>
       <c r="AK4" t="n">
-        <v>3854000</v>
+        <v>385000</v>
       </c>
       <c r="AL4" t="n">
-        <v>3712000</v>
+        <v>13358000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1503000</v>
+        <v>-3094000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-9391000</v>
+        <v>-5135000</v>
       </c>
       <c r="AO4" t="n">
-        <v>8030000</v>
+        <v>-4744000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1413000</v>
+        <v>2378000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-433000</v>
+        <v>-1135000</v>
       </c>
       <c r="AS4" t="n">
-        <v>27697000</v>
+        <v>31277000</v>
       </c>
       <c r="AT4" t="n">
-        <v>345000</v>
+        <v>752000</v>
       </c>
       <c r="AU4" t="n">
-        <v>27352000</v>
+        <v>30525000</v>
       </c>
       <c r="AV4" t="n">
-        <v>-198000</v>
+        <v>-137000</v>
       </c>
       <c r="AW4" t="n">
-        <v>154000</v>
+        <v>217000</v>
       </c>
       <c r="AX4" t="n">
-        <v>18776000</v>
+        <v>-19650000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>8357000</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>59638000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-416000</v>
+      </c>
       <c r="D5" t="n">
-        <v>-7541000</v>
+        <v>-15650000</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
+        <v>2939000</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>-36186000</v>
+        <v>-21922000</v>
       </c>
       <c r="H5" t="n">
-        <v>102101000</v>
+        <v>72825000</v>
       </c>
       <c r="I5" t="n">
-        <v>114743000</v>
+        <v>34221000</v>
       </c>
       <c r="J5" t="n">
-        <v>-129000</v>
+        <v>-1653000</v>
       </c>
       <c r="K5" t="n">
-        <v>-12513000</v>
+        <v>40257000</v>
       </c>
       <c r="L5" t="n">
-        <v>-21685000</v>
+        <v>-27930000</v>
       </c>
       <c r="M5" t="n">
-        <v>-2253000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-1500000</v>
-      </c>
+        <v>-2364000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>-1500000</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
+        <v>-416000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-416000</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>-7541000</v>
+        <v>-12711000</v>
       </c>
       <c r="T5" t="n">
-        <v>-7541000</v>
+        <v>-12711000</v>
       </c>
       <c r="U5" t="n">
-        <v>-7541000</v>
+        <v>-15650000</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2939000</v>
       </c>
       <c r="W5" t="n">
-        <v>-35371000</v>
-      </c>
-      <c r="X5" t="inlineStr"/>
+        <v>-13373000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>10421000</v>
+      </c>
       <c r="Y5" t="n">
-        <v>264000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
+        <v>442000</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>-3119000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-732000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-732000</v>
-      </c>
+        <v>-3119000</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>-34903000</v>
+        <v>-21117000</v>
       </c>
       <c r="AG5" t="n">
-        <v>551000</v>
+        <v>805000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-35454000</v>
+        <v>-21922000</v>
       </c>
       <c r="AI5" t="n">
-        <v>44543000</v>
+        <v>81560000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-1432000</v>
+        <v>-7917000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-4368000</v>
+        <v>-25697000</v>
       </c>
       <c r="AL5" t="n">
-        <v>31780000</v>
+        <v>20191000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-5173000</v>
+        <v>-9814000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-13845000</v>
+        <v>-19394000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-17130000</v>
+        <v>-16680000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1540000</v>
+        <v>1789000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>782000</v>
+        <v>3248000</v>
       </c>
       <c r="AS5" t="n">
-        <v>27069000</v>
+        <v>33821000</v>
       </c>
       <c r="AT5" t="n">
-        <v>38000</v>
+        <v>89000</v>
       </c>
       <c r="AU5" t="n">
-        <v>27031000</v>
+        <v>33732000</v>
       </c>
       <c r="AV5" t="n">
-        <v>-195000</v>
+        <v>-127000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-183000</v>
+        <v>-177000</v>
       </c>
       <c r="AX5" t="n">
-        <v>21254000</v>
+        <v>74747000</v>
       </c>
     </row>
   </sheetData>
@@ -3778,187 +3778,187 @@
       </c>
       <c r="DB1" t="inlineStr">
         <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
       <c r="EM1" t="inlineStr">
@@ -4097,7 +4097,7 @@
         <v>0.2717</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.712</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="AH2" t="n">
         <v>2.7</v>
@@ -4109,7 +4109,7 @@
         <v>1610000</v>
       </c>
       <c r="AK2" t="n">
-        <v>493500</v>
+        <v>341016</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -4145,10 +4145,10 @@
         <v>0.29585162</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.08068</v>
+        <v>0.081</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.092265</v>
+        <v>0.09041</v>
       </c>
       <c r="AY2" t="n">
         <v>0.008</v>
@@ -4216,10 +4216,10 @@
         <v>1.698</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.012500048</v>
+        <v>-0.04705882</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BV2" t="n">
         <v>0.0075</v>
@@ -4335,140 +4335,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DB2" t="n">
+        <v>3.846152</v>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DD2" t="n">
+        <v>0.0029999986</v>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>0.079 - 0.083</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DG2" t="n">
+        <v>341016</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>0.021000002</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0.35000002</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>0.06 - 0.124</t>
+        </is>
+      </c>
+      <c r="DK2" t="n">
+        <v>-0.042999998</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>-0.3467742</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-4.705882</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>1743429461</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>1743429461</v>
+      </c>
+      <c r="DP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>-0.009410000999999999</v>
+      </c>
+      <c r="DU2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DC2" t="n">
+      <c r="DV2" t="n">
         <v>1774857405</v>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DW2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>finmb_655149242</t>
         </is>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DY2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DZ2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DH2" t="n">
+      <c r="EA2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DI2" t="inlineStr">
+      <c r="EB2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DK2" t="inlineStr">
+      <c r="EC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>Cirtek Holdings Limited</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
         <is>
           <t>CIRTEK HLDGS</t>
         </is>
       </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>Cirtek Holdings Limited</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DN2" t="n">
-        <v>0.00032000244</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>0.003966317</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.011265002</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-0.12209399</v>
-      </c>
-      <c r="DR2" t="n">
+      <c r="EG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>1583976600000</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>-0.10408142</v>
+      </c>
+      <c r="EJ2" t="n">
         <v>15</v>
       </c>
-      <c r="DS2" t="n">
+      <c r="EK2" t="n">
         <v>15</v>
       </c>
-      <c r="DT2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>3.846152</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="DW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>1583976600000</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>0.0029999986</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>0.079 - 0.083</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="EB2" t="n">
-        <v>493500</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0.021000002</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>0.35000002</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>0.06 - 0.124</t>
-        </is>
-      </c>
-      <c r="EF2" t="n">
-        <v>-0.042999998</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>-0.3467742</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>1.2500048</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>1743429461</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>1743429461</v>
-      </c>
-      <c r="EK2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>0.03</v>
+      <c r="EL2" t="b">
+        <v>0</v>
       </c>
       <c r="EM2" t="inlineStr"/>
     </row>
